--- a/artfynd/A 45979-2023 artfynd.xlsx
+++ b/artfynd/A 45979-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45979-2023 artfynd.xlsx
+++ b/artfynd/A 45979-2023 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117769299</v>
+        <v>117769385</v>
       </c>
       <c r="B4" t="n">
-        <v>97746</v>
+        <v>97859</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223572</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117769385</v>
+        <v>117769299</v>
       </c>
       <c r="B5" t="n">
-        <v>97859</v>
+        <v>97746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>223572</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 45979-2023 artfynd.xlsx
+++ b/artfynd/A 45979-2023 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117769385</v>
+        <v>117769288</v>
       </c>
       <c r="B4" t="n">
-        <v>97859</v>
+        <v>97746</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>219788</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1011,7 +1011,7 @@
         <v>117769299</v>
       </c>
       <c r="B5" t="n">
-        <v>97746</v>
+        <v>97748</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117769288</v>
+        <v>117769385</v>
       </c>
       <c r="B6" t="n">
-        <v>97744</v>
+        <v>97861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219788</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 45979-2023 artfynd.xlsx
+++ b/artfynd/A 45979-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110206159</v>
+        <v>110102159</v>
       </c>
       <c r="B2" t="n">
-        <v>40972</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485409.6902719922</v>
+        <v>485511</v>
       </c>
       <c r="R2" t="n">
-        <v>6996757.829817138</v>
+        <v>6996814</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,37 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110206278</v>
+        <v>110206159</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485435.6351005657</v>
+        <v>485410</v>
       </c>
       <c r="R3" t="n">
-        <v>6996779.449655245</v>
+        <v>6996758</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +852,9 @@
           <t>2023-06-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,57 +881,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117769288</v>
+        <v>117767779</v>
       </c>
       <c r="B4" t="n">
-        <v>97748</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219788</v>
+        <v>101248</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bye, Jmt</t>
+          <t>Bye, Bye, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485283</v>
+        <v>485295</v>
       </c>
       <c r="R4" t="n">
-        <v>6996672</v>
+        <v>6996677</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +960,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1008,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117769385</v>
+        <v>117769288</v>
       </c>
       <c r="B5" t="n">
-        <v>97863</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>219788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1115,15 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117769299</v>
+        <v>117769385</v>
       </c>
       <c r="B6" t="n">
-        <v>97750</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1091,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223572</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1220,6 +1180,303 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>117767784</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99145</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222118</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Flugblomster</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ophrys insectifera</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bye, Bye, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>485295</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6996677</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Bodil Carlsson, Thomas Stålhandske, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>110206278</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bye kalkbarrskogs naturreservat, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>485435</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6996779</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>117769299</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99028</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223572</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blodnycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. cruenta</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(O F.Müll.) Hyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bye, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>485283</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6996672</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Bodil Carlsson, Thomas Stålhandske, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45979-2023 artfynd.xlsx
+++ b/artfynd/A 45979-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110102159</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110206159</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117767779</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117769288</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117769385</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1276,6 +1306,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117767784</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1374,6 +1409,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110206278</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,8 +1516,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117769299</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>